--- a/api/sieve.xlsx
+++ b/api/sieve.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\programing_lang\web\projects\materials\project1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\programing_lang\web\projects\materials\project1\api\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3644275-62C8-4F88-9001-23D601B81D62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED8E1DA-7994-4642-8CEB-9B0E729D97FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="601" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="61">
   <si>
     <t>Result</t>
   </si>
@@ -276,9 +276,6 @@
   </si>
   <si>
     <t>File No.: 5143</t>
-  </si>
-  <si>
-    <t>Date :08/09/2025</t>
   </si>
 </sst>
 </file>
@@ -1482,7 +1479,6 @@
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1519,12 +1515,87 @@
     <xf numFmtId="165" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="34" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1537,9 +1608,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1585,77 +1653,62 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="34" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="167" fontId="35" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1706,64 +1759,31 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="35" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1810,29 +1830,8 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -2965,121 +2964,121 @@
   <sheetData>
     <row r="1" spans="1:38" ht="20.100000000000001" customHeight="1">
       <c r="A1" s="36"/>
-      <c r="B1" s="160" t="s">
+      <c r="B1" s="156" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="160"/>
-      <c r="D1" s="160"/>
-      <c r="E1" s="160"/>
-      <c r="F1" s="160"/>
-      <c r="G1" s="160"/>
-      <c r="H1" s="160"/>
-      <c r="I1" s="160"/>
-      <c r="J1" s="160"/>
-      <c r="K1" s="160"/>
-      <c r="L1" s="160"/>
-      <c r="M1" s="160"/>
-      <c r="N1" s="160"/>
-      <c r="O1" s="160"/>
-      <c r="P1" s="160"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
+      <c r="F1" s="156"/>
+      <c r="G1" s="156"/>
+      <c r="H1" s="156"/>
+      <c r="I1" s="156"/>
+      <c r="J1" s="156"/>
+      <c r="K1" s="156"/>
+      <c r="L1" s="156"/>
+      <c r="M1" s="156"/>
+      <c r="N1" s="156"/>
+      <c r="O1" s="156"/>
+      <c r="P1" s="156"/>
       <c r="Q1" s="37"/>
     </row>
     <row r="2" spans="1:38" ht="15.9" customHeight="1">
       <c r="A2" s="38"/>
-      <c r="B2" s="144" t="s">
+      <c r="B2" s="157" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="144"/>
-      <c r="D2" s="144"/>
-      <c r="E2" s="144"/>
-      <c r="F2" s="144"/>
-      <c r="G2" s="144"/>
-      <c r="H2" s="144"/>
-      <c r="I2" s="144"/>
-      <c r="J2" s="144"/>
-      <c r="K2" s="144"/>
-      <c r="L2" s="144"/>
-      <c r="M2" s="144"/>
-      <c r="N2" s="144"/>
-      <c r="O2" s="144"/>
-      <c r="P2" s="144"/>
+      <c r="C2" s="157"/>
+      <c r="D2" s="157"/>
+      <c r="E2" s="157"/>
+      <c r="F2" s="157"/>
+      <c r="G2" s="157"/>
+      <c r="H2" s="157"/>
+      <c r="I2" s="157"/>
+      <c r="J2" s="157"/>
+      <c r="K2" s="157"/>
+      <c r="L2" s="157"/>
+      <c r="M2" s="157"/>
+      <c r="N2" s="157"/>
+      <c r="O2" s="157"/>
+      <c r="P2" s="157"/>
       <c r="Q2" s="39"/>
     </row>
     <row r="3" spans="1:38" ht="15.9" customHeight="1">
       <c r="A3" s="38"/>
-      <c r="B3" s="144" t="s">
+      <c r="B3" s="157" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="144"/>
-      <c r="D3" s="144"/>
-      <c r="E3" s="144"/>
-      <c r="F3" s="144"/>
-      <c r="G3" s="144"/>
-      <c r="H3" s="144"/>
-      <c r="I3" s="144"/>
-      <c r="J3" s="144"/>
-      <c r="K3" s="144"/>
-      <c r="L3" s="144"/>
-      <c r="M3" s="144"/>
-      <c r="N3" s="144"/>
-      <c r="O3" s="144"/>
-      <c r="P3" s="144"/>
+      <c r="C3" s="157"/>
+      <c r="D3" s="157"/>
+      <c r="E3" s="157"/>
+      <c r="F3" s="157"/>
+      <c r="G3" s="157"/>
+      <c r="H3" s="157"/>
+      <c r="I3" s="157"/>
+      <c r="J3" s="157"/>
+      <c r="K3" s="157"/>
+      <c r="L3" s="157"/>
+      <c r="M3" s="157"/>
+      <c r="N3" s="157"/>
+      <c r="O3" s="157"/>
+      <c r="P3" s="157"/>
       <c r="Q3" s="39"/>
     </row>
     <row r="4" spans="1:38" ht="15.9" customHeight="1">
       <c r="A4" s="38"/>
-      <c r="B4" s="161" t="s">
+      <c r="B4" s="158" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="161"/>
-      <c r="D4" s="161"/>
-      <c r="E4" s="161"/>
-      <c r="F4" s="161"/>
-      <c r="G4" s="161"/>
-      <c r="H4" s="161"/>
-      <c r="I4" s="161"/>
-      <c r="J4" s="161"/>
-      <c r="K4" s="161"/>
-      <c r="L4" s="161"/>
-      <c r="M4" s="161"/>
-      <c r="N4" s="161"/>
-      <c r="O4" s="161"/>
-      <c r="P4" s="161"/>
+      <c r="C4" s="158"/>
+      <c r="D4" s="158"/>
+      <c r="E4" s="158"/>
+      <c r="F4" s="158"/>
+      <c r="G4" s="158"/>
+      <c r="H4" s="158"/>
+      <c r="I4" s="158"/>
+      <c r="J4" s="158"/>
+      <c r="K4" s="158"/>
+      <c r="L4" s="158"/>
+      <c r="M4" s="158"/>
+      <c r="N4" s="158"/>
+      <c r="O4" s="158"/>
+      <c r="P4" s="158"/>
       <c r="Q4" s="39"/>
     </row>
     <row r="5" spans="1:38" ht="15.9" customHeight="1">
       <c r="A5" s="40"/>
-      <c r="B5" s="162" t="s">
+      <c r="B5" s="159" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="162"/>
-      <c r="D5" s="162"/>
-      <c r="E5" s="162"/>
-      <c r="F5" s="162"/>
-      <c r="G5" s="162"/>
-      <c r="H5" s="162"/>
-      <c r="I5" s="162"/>
-      <c r="J5" s="162"/>
-      <c r="K5" s="162"/>
-      <c r="L5" s="162"/>
-      <c r="M5" s="162"/>
-      <c r="N5" s="162"/>
-      <c r="O5" s="162"/>
-      <c r="P5" s="162"/>
+      <c r="C5" s="159"/>
+      <c r="D5" s="159"/>
+      <c r="E5" s="159"/>
+      <c r="F5" s="159"/>
+      <c r="G5" s="159"/>
+      <c r="H5" s="159"/>
+      <c r="I5" s="159"/>
+      <c r="J5" s="159"/>
+      <c r="K5" s="159"/>
+      <c r="L5" s="159"/>
+      <c r="M5" s="159"/>
+      <c r="N5" s="159"/>
+      <c r="O5" s="159"/>
+      <c r="P5" s="159"/>
       <c r="Q5" s="41"/>
     </row>
     <row r="6" spans="1:38" ht="15.9" customHeight="1">
       <c r="A6" s="38"/>
-      <c r="B6" s="167" t="s">
+      <c r="B6" s="137" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="167"/>
-      <c r="D6" s="167"/>
-      <c r="E6" s="167"/>
-      <c r="F6" s="167"/>
-      <c r="G6" s="167"/>
-      <c r="H6" s="167"/>
-      <c r="I6" s="167"/>
+      <c r="C6" s="137"/>
+      <c r="D6" s="137"/>
+      <c r="E6" s="137"/>
+      <c r="F6" s="137"/>
+      <c r="G6" s="137"/>
+      <c r="H6" s="137"/>
+      <c r="I6" s="137"/>
       <c r="O6" s="3" t="s">
         <v>42</v>
       </c>
@@ -3087,92 +3086,92 @@
     </row>
     <row r="7" spans="1:38" ht="19.5" customHeight="1">
       <c r="A7" s="40"/>
-      <c r="B7" s="168" t="s">
+      <c r="B7" s="138" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="169"/>
-      <c r="D7" s="169"/>
-      <c r="E7" s="169"/>
-      <c r="F7" s="169"/>
-      <c r="G7" s="169"/>
-      <c r="H7" s="169"/>
-      <c r="I7" s="169"/>
-      <c r="J7" s="169"/>
-      <c r="K7" s="169"/>
-      <c r="L7" s="169"/>
+      <c r="C7" s="139"/>
+      <c r="D7" s="139"/>
+      <c r="E7" s="139"/>
+      <c r="F7" s="139"/>
+      <c r="G7" s="139"/>
+      <c r="H7" s="139"/>
+      <c r="I7" s="139"/>
+      <c r="J7" s="139"/>
+      <c r="K7" s="139"/>
+      <c r="L7" s="139"/>
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
       <c r="O7" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="P7" s="179">
+      <c r="P7" s="149">
         <f>F11+6</f>
         <v>45906</v>
       </c>
-      <c r="Q7" s="180"/>
+      <c r="Q7" s="150"/>
     </row>
     <row r="8" spans="1:38" ht="19.2" customHeight="1">
-      <c r="A8" s="170" t="s">
+      <c r="A8" s="140" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="171"/>
-      <c r="C8" s="171"/>
-      <c r="D8" s="171"/>
-      <c r="E8" s="171"/>
-      <c r="F8" s="171"/>
-      <c r="G8" s="171"/>
-      <c r="H8" s="171"/>
-      <c r="I8" s="171"/>
-      <c r="J8" s="171"/>
-      <c r="K8" s="171"/>
-      <c r="L8" s="171"/>
-      <c r="M8" s="171"/>
-      <c r="N8" s="171"/>
-      <c r="O8" s="171"/>
-      <c r="P8" s="171"/>
-      <c r="Q8" s="172"/>
+      <c r="B8" s="141"/>
+      <c r="C8" s="141"/>
+      <c r="D8" s="141"/>
+      <c r="E8" s="141"/>
+      <c r="F8" s="141"/>
+      <c r="G8" s="141"/>
+      <c r="H8" s="141"/>
+      <c r="I8" s="141"/>
+      <c r="J8" s="141"/>
+      <c r="K8" s="141"/>
+      <c r="L8" s="141"/>
+      <c r="M8" s="141"/>
+      <c r="N8" s="141"/>
+      <c r="O8" s="141"/>
+      <c r="P8" s="141"/>
+      <c r="Q8" s="142"/>
     </row>
     <row r="9" spans="1:38" ht="34.799999999999997" customHeight="1">
-      <c r="A9" s="173" t="s">
+      <c r="A9" s="143" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="174"/>
-      <c r="C9" s="174"/>
-      <c r="D9" s="174"/>
-      <c r="E9" s="174"/>
-      <c r="F9" s="174"/>
-      <c r="G9" s="174"/>
-      <c r="H9" s="174"/>
-      <c r="I9" s="174"/>
-      <c r="J9" s="174"/>
-      <c r="K9" s="174"/>
-      <c r="L9" s="174"/>
-      <c r="M9" s="174"/>
-      <c r="N9" s="174"/>
-      <c r="O9" s="174"/>
-      <c r="P9" s="174"/>
-      <c r="Q9" s="175"/>
+      <c r="B9" s="144"/>
+      <c r="C9" s="144"/>
+      <c r="D9" s="144"/>
+      <c r="E9" s="144"/>
+      <c r="F9" s="144"/>
+      <c r="G9" s="144"/>
+      <c r="H9" s="144"/>
+      <c r="I9" s="144"/>
+      <c r="J9" s="144"/>
+      <c r="K9" s="144"/>
+      <c r="L9" s="144"/>
+      <c r="M9" s="144"/>
+      <c r="N9" s="144"/>
+      <c r="O9" s="144"/>
+      <c r="P9" s="144"/>
+      <c r="Q9" s="145"/>
     </row>
     <row r="10" spans="1:38" ht="36" customHeight="1">
-      <c r="A10" s="176" t="s">
+      <c r="A10" s="146" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="177"/>
-      <c r="C10" s="177"/>
-      <c r="D10" s="177"/>
-      <c r="E10" s="177"/>
-      <c r="F10" s="177"/>
-      <c r="G10" s="177"/>
-      <c r="H10" s="177"/>
-      <c r="I10" s="177"/>
-      <c r="J10" s="177"/>
-      <c r="K10" s="177"/>
-      <c r="L10" s="177"/>
-      <c r="M10" s="177"/>
-      <c r="N10" s="177"/>
-      <c r="O10" s="177"/>
-      <c r="P10" s="177"/>
-      <c r="Q10" s="178"/>
+      <c r="B10" s="147"/>
+      <c r="C10" s="147"/>
+      <c r="D10" s="147"/>
+      <c r="E10" s="147"/>
+      <c r="F10" s="147"/>
+      <c r="G10" s="147"/>
+      <c r="H10" s="147"/>
+      <c r="I10" s="147"/>
+      <c r="J10" s="147"/>
+      <c r="K10" s="147"/>
+      <c r="L10" s="147"/>
+      <c r="M10" s="147"/>
+      <c r="N10" s="147"/>
+      <c r="O10" s="147"/>
+      <c r="P10" s="147"/>
+      <c r="Q10" s="148"/>
       <c r="AF10" s="23"/>
       <c r="AG10" s="23"/>
       <c r="AH10" s="23"/>
@@ -3183,17 +3182,17 @@
     </row>
     <row r="11" spans="1:38" ht="20.100000000000001" customHeight="1">
       <c r="A11" s="38"/>
-      <c r="B11" s="163" t="s">
+      <c r="B11" s="152" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="164"/>
-      <c r="D11" s="164"/>
-      <c r="E11" s="164"/>
-      <c r="F11" s="165">
+      <c r="C11" s="153"/>
+      <c r="D11" s="153"/>
+      <c r="E11" s="153"/>
+      <c r="F11" s="154">
         <v>45900</v>
       </c>
-      <c r="G11" s="165"/>
-      <c r="H11" s="165"/>
+      <c r="G11" s="154"/>
+      <c r="H11" s="154"/>
       <c r="I11" s="42"/>
       <c r="J11" s="42"/>
       <c r="K11" s="42"/>
@@ -3202,43 +3201,43 @@
     </row>
     <row r="12" spans="1:38" ht="15.9" customHeight="1">
       <c r="A12" s="38"/>
-      <c r="B12" s="166" t="s">
+      <c r="B12" s="155" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="166"/>
-      <c r="D12" s="166"/>
-      <c r="E12" s="166"/>
-      <c r="F12" s="139" t="s">
+      <c r="C12" s="155"/>
+      <c r="D12" s="155"/>
+      <c r="E12" s="155"/>
+      <c r="F12" s="151" t="s">
         <v>45</v>
       </c>
-      <c r="G12" s="139"/>
-      <c r="H12" s="139"/>
-      <c r="I12" s="139"/>
-      <c r="J12" s="139"/>
-      <c r="K12" s="139"/>
-      <c r="L12" s="139"/>
-      <c r="N12" s="139" t="s">
+      <c r="G12" s="151"/>
+      <c r="H12" s="151"/>
+      <c r="I12" s="151"/>
+      <c r="J12" s="151"/>
+      <c r="K12" s="151"/>
+      <c r="L12" s="151"/>
+      <c r="N12" s="151" t="s">
         <v>3</v>
       </c>
-      <c r="O12" s="139"/>
-      <c r="P12" s="139"/>
+      <c r="O12" s="151"/>
+      <c r="P12" s="151"/>
       <c r="Q12" s="39"/>
     </row>
     <row r="13" spans="1:38" ht="15.9" customHeight="1">
       <c r="A13" s="38"/>
-      <c r="B13" s="138" t="s">
+      <c r="B13" s="160" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="138"/>
-      <c r="D13" s="138"/>
-      <c r="E13" s="138"/>
-      <c r="F13" s="138"/>
-      <c r="G13" s="138"/>
-      <c r="H13" s="138"/>
-      <c r="I13" s="139" t="s">
+      <c r="C13" s="160"/>
+      <c r="D13" s="160"/>
+      <c r="E13" s="160"/>
+      <c r="F13" s="160"/>
+      <c r="G13" s="160"/>
+      <c r="H13" s="160"/>
+      <c r="I13" s="151" t="s">
         <v>49</v>
       </c>
-      <c r="J13" s="139"/>
+      <c r="J13" s="151"/>
       <c r="K13" s="22"/>
       <c r="N13" s="44" t="s">
         <v>4</v>
@@ -3251,11 +3250,11 @@
     </row>
     <row r="14" spans="1:38" ht="15.9" customHeight="1">
       <c r="A14" s="38"/>
-      <c r="B14" s="145" t="s">
+      <c r="B14" s="165" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="146"/>
-      <c r="D14" s="146"/>
+      <c r="C14" s="166"/>
+      <c r="D14" s="166"/>
       <c r="E14" s="46">
         <v>3</v>
       </c>
@@ -3276,11 +3275,11 @@
     </row>
     <row r="15" spans="1:38" ht="15.9" customHeight="1">
       <c r="A15" s="38"/>
-      <c r="B15" s="146" t="s">
+      <c r="B15" s="166" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="146"/>
-      <c r="D15" s="146"/>
+      <c r="C15" s="166"/>
+      <c r="D15" s="166"/>
       <c r="E15" s="46">
         <v>50</v>
       </c>
@@ -3288,33 +3287,33 @@
         <v>6</v>
       </c>
       <c r="O15" s="35"/>
-      <c r="P15" s="135">
+      <c r="P15" s="134">
         <v>0</v>
       </c>
       <c r="Q15" s="39"/>
     </row>
     <row r="16" spans="1:38" ht="15.9" customHeight="1" thickBot="1">
       <c r="A16" s="38"/>
-      <c r="B16" s="149" t="s">
+      <c r="B16" s="169" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="149"/>
-      <c r="D16" s="149"/>
-      <c r="E16" s="147">
+      <c r="C16" s="169"/>
+      <c r="D16" s="169"/>
+      <c r="E16" s="167">
         <f>500*(E15-1)</f>
         <v>24500</v>
       </c>
-      <c r="F16" s="147"/>
+      <c r="F16" s="167"/>
       <c r="G16" s="27"/>
       <c r="H16" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="I16" s="148">
+      <c r="I16" s="168">
         <f>E15*500</f>
         <v>25000</v>
       </c>
-      <c r="J16" s="148"/>
-      <c r="K16" s="148"/>
+      <c r="J16" s="168"/>
+      <c r="K16" s="168"/>
       <c r="L16" s="1" t="s">
         <v>41</v>
       </c>
@@ -3325,11 +3324,11 @@
     </row>
     <row r="17" spans="1:17" ht="45" customHeight="1" thickTop="1" thickBot="1">
       <c r="A17" s="38"/>
-      <c r="B17" s="140" t="s">
+      <c r="B17" s="161" t="s">
         <v>2</v>
       </c>
-      <c r="C17" s="141"/>
-      <c r="D17" s="142"/>
+      <c r="C17" s="162"/>
+      <c r="D17" s="163"/>
       <c r="E17" s="8">
         <v>100</v>
       </c>
@@ -3370,11 +3369,11 @@
     </row>
     <row r="18" spans="1:17" ht="33.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="A18" s="38"/>
-      <c r="B18" s="150" t="s">
+      <c r="B18" s="170" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="151"/>
-      <c r="D18" s="152"/>
+      <c r="C18" s="171"/>
+      <c r="D18" s="172"/>
       <c r="E18" s="24">
         <v>100</v>
       </c>
@@ -3415,26 +3414,26 @@
     </row>
     <row r="19" spans="1:17" ht="36" customHeight="1" thickTop="1" thickBot="1">
       <c r="A19" s="38"/>
-      <c r="B19" s="140" t="s">
+      <c r="B19" s="161" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="141"/>
-      <c r="D19" s="142"/>
+      <c r="C19" s="162"/>
+      <c r="D19" s="163"/>
       <c r="E19" s="8">
         <v>100</v>
       </c>
-      <c r="F19" s="157" t="s">
+      <c r="F19" s="177" t="s">
         <v>34</v>
       </c>
-      <c r="G19" s="158"/>
-      <c r="H19" s="158"/>
-      <c r="I19" s="158"/>
-      <c r="J19" s="158"/>
-      <c r="K19" s="158"/>
-      <c r="L19" s="158"/>
-      <c r="M19" s="158"/>
-      <c r="N19" s="158"/>
-      <c r="O19" s="159"/>
+      <c r="G19" s="178"/>
+      <c r="H19" s="178"/>
+      <c r="I19" s="178"/>
+      <c r="J19" s="178"/>
+      <c r="K19" s="178"/>
+      <c r="L19" s="178"/>
+      <c r="M19" s="178"/>
+      <c r="N19" s="178"/>
+      <c r="O19" s="179"/>
       <c r="P19" s="25">
         <v>30</v>
       </c>
@@ -3506,23 +3505,23 @@
     </row>
     <row r="36" spans="1:19" ht="33" customHeight="1">
       <c r="A36" s="38"/>
-      <c r="B36" s="153" t="s">
+      <c r="B36" s="173" t="s">
         <v>40</v>
       </c>
-      <c r="C36" s="154"/>
-      <c r="D36" s="154"/>
-      <c r="E36" s="154"/>
-      <c r="F36" s="154"/>
-      <c r="G36" s="154"/>
-      <c r="H36" s="154"/>
-      <c r="I36" s="154"/>
-      <c r="J36" s="154"/>
-      <c r="K36" s="154"/>
-      <c r="L36" s="154"/>
-      <c r="M36" s="154"/>
-      <c r="N36" s="154"/>
-      <c r="O36" s="154"/>
-      <c r="P36" s="155"/>
+      <c r="C36" s="174"/>
+      <c r="D36" s="174"/>
+      <c r="E36" s="174"/>
+      <c r="F36" s="174"/>
+      <c r="G36" s="174"/>
+      <c r="H36" s="174"/>
+      <c r="I36" s="174"/>
+      <c r="J36" s="174"/>
+      <c r="K36" s="174"/>
+      <c r="L36" s="174"/>
+      <c r="M36" s="174"/>
+      <c r="N36" s="174"/>
+      <c r="O36" s="174"/>
+      <c r="P36" s="175"/>
       <c r="Q36" s="39"/>
     </row>
     <row r="37" spans="1:19" ht="15.9" customHeight="1">
@@ -3534,23 +3533,23 @@
     </row>
     <row r="38" spans="1:19" ht="45" customHeight="1">
       <c r="A38" s="40"/>
-      <c r="B38" s="156" t="s">
+      <c r="B38" s="176" t="s">
         <v>31</v>
       </c>
-      <c r="C38" s="156"/>
-      <c r="D38" s="156"/>
-      <c r="E38" s="156"/>
-      <c r="F38" s="156"/>
-      <c r="G38" s="156"/>
-      <c r="H38" s="156"/>
-      <c r="I38" s="156"/>
-      <c r="J38" s="156"/>
-      <c r="K38" s="156"/>
-      <c r="L38" s="156"/>
-      <c r="M38" s="156"/>
-      <c r="N38" s="156"/>
-      <c r="O38" s="156"/>
-      <c r="P38" s="156"/>
+      <c r="C38" s="176"/>
+      <c r="D38" s="176"/>
+      <c r="E38" s="176"/>
+      <c r="F38" s="176"/>
+      <c r="G38" s="176"/>
+      <c r="H38" s="176"/>
+      <c r="I38" s="176"/>
+      <c r="J38" s="176"/>
+      <c r="K38" s="176"/>
+      <c r="L38" s="176"/>
+      <c r="M38" s="176"/>
+      <c r="N38" s="176"/>
+      <c r="O38" s="176"/>
+      <c r="P38" s="176"/>
       <c r="Q38" s="41"/>
     </row>
     <row r="39" spans="1:19" ht="13.2" customHeight="1">
@@ -3574,23 +3573,23 @@
     </row>
     <row r="40" spans="1:19" ht="19.2" customHeight="1">
       <c r="A40" s="38"/>
-      <c r="B40" s="143" t="s">
+      <c r="B40" s="164" t="s">
         <v>30</v>
       </c>
-      <c r="C40" s="143"/>
-      <c r="D40" s="143"/>
-      <c r="E40" s="143"/>
-      <c r="F40" s="143"/>
-      <c r="G40" s="143"/>
-      <c r="H40" s="143"/>
-      <c r="K40" s="144" t="s">
+      <c r="C40" s="164"/>
+      <c r="D40" s="164"/>
+      <c r="E40" s="164"/>
+      <c r="F40" s="164"/>
+      <c r="G40" s="164"/>
+      <c r="H40" s="164"/>
+      <c r="K40" s="157" t="s">
         <v>27</v>
       </c>
-      <c r="L40" s="144"/>
-      <c r="M40" s="144"/>
-      <c r="N40" s="144"/>
-      <c r="O40" s="144"/>
-      <c r="P40" s="144"/>
+      <c r="L40" s="157"/>
+      <c r="M40" s="157"/>
+      <c r="N40" s="157"/>
+      <c r="O40" s="157"/>
+      <c r="P40" s="157"/>
       <c r="Q40" s="39"/>
     </row>
     <row r="41" spans="1:19" ht="13.2" customHeight="1" thickBot="1">
@@ -3645,22 +3644,6 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <mergeCells count="31">
-    <mergeCell ref="B6:I6"/>
-    <mergeCell ref="B7:L7"/>
-    <mergeCell ref="A8:Q8"/>
-    <mergeCell ref="A9:Q9"/>
-    <mergeCell ref="A10:Q10"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="F12:L12"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B1:P1"/>
-    <mergeCell ref="B2:P2"/>
-    <mergeCell ref="B3:P3"/>
-    <mergeCell ref="B4:P4"/>
-    <mergeCell ref="B5:P5"/>
     <mergeCell ref="B13:H13"/>
     <mergeCell ref="I13:J13"/>
     <mergeCell ref="B17:D17"/>
@@ -3676,6 +3659,22 @@
     <mergeCell ref="B38:P38"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="F19:O19"/>
+    <mergeCell ref="B1:P1"/>
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="B3:P3"/>
+    <mergeCell ref="B4:P4"/>
+    <mergeCell ref="B5:P5"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="F12:L12"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="B6:I6"/>
+    <mergeCell ref="B7:L7"/>
+    <mergeCell ref="A8:Q8"/>
+    <mergeCell ref="A9:Q9"/>
+    <mergeCell ref="A10:Q10"/>
+    <mergeCell ref="P7:Q7"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="P13">
@@ -3717,162 +3716,162 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:256" ht="17.399999999999999">
-      <c r="A1" s="199" t="s">
+      <c r="A1" s="180" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="200"/>
-      <c r="C1" s="200"/>
-      <c r="D1" s="200"/>
-      <c r="E1" s="200"/>
-      <c r="F1" s="200"/>
-      <c r="G1" s="200"/>
-      <c r="H1" s="200"/>
-      <c r="I1" s="200"/>
-      <c r="J1" s="200"/>
-      <c r="K1" s="201"/>
+      <c r="B1" s="181"/>
+      <c r="C1" s="181"/>
+      <c r="D1" s="181"/>
+      <c r="E1" s="181"/>
+      <c r="F1" s="181"/>
+      <c r="G1" s="181"/>
+      <c r="H1" s="181"/>
+      <c r="I1" s="181"/>
+      <c r="J1" s="181"/>
+      <c r="K1" s="182"/>
     </row>
     <row r="2" spans="1:256" ht="15.6" customHeight="1">
-      <c r="A2" s="202" t="s">
+      <c r="A2" s="183" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="203"/>
-      <c r="C2" s="203"/>
-      <c r="D2" s="203"/>
-      <c r="E2" s="203"/>
-      <c r="F2" s="203"/>
-      <c r="G2" s="203"/>
-      <c r="H2" s="203"/>
-      <c r="I2" s="203"/>
-      <c r="J2" s="203"/>
-      <c r="K2" s="204"/>
+      <c r="B2" s="184"/>
+      <c r="C2" s="184"/>
+      <c r="D2" s="184"/>
+      <c r="E2" s="184"/>
+      <c r="F2" s="184"/>
+      <c r="G2" s="184"/>
+      <c r="H2" s="184"/>
+      <c r="I2" s="184"/>
+      <c r="J2" s="184"/>
+      <c r="K2" s="185"/>
     </row>
     <row r="3" spans="1:256" ht="15.6" customHeight="1">
-      <c r="A3" s="202" t="s">
+      <c r="A3" s="183" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="203"/>
-      <c r="C3" s="203"/>
-      <c r="D3" s="203"/>
-      <c r="E3" s="203"/>
-      <c r="F3" s="203"/>
-      <c r="G3" s="203"/>
-      <c r="H3" s="203"/>
-      <c r="I3" s="203"/>
-      <c r="J3" s="203"/>
-      <c r="K3" s="204"/>
+      <c r="B3" s="184"/>
+      <c r="C3" s="184"/>
+      <c r="D3" s="184"/>
+      <c r="E3" s="184"/>
+      <c r="F3" s="184"/>
+      <c r="G3" s="184"/>
+      <c r="H3" s="184"/>
+      <c r="I3" s="184"/>
+      <c r="J3" s="184"/>
+      <c r="K3" s="185"/>
     </row>
     <row r="4" spans="1:256" s="21" customFormat="1" ht="15.9" customHeight="1">
       <c r="A4" s="28"/>
-      <c r="B4" s="181" t="s">
+      <c r="B4" s="199" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="181"/>
-      <c r="D4" s="181"/>
-      <c r="E4" s="181"/>
-      <c r="F4" s="181"/>
-      <c r="G4" s="181"/>
-      <c r="H4" s="181"/>
-      <c r="I4" s="181"/>
-      <c r="J4" s="181"/>
+      <c r="C4" s="199"/>
+      <c r="D4" s="199"/>
+      <c r="E4" s="199"/>
+      <c r="F4" s="199"/>
+      <c r="G4" s="199"/>
+      <c r="H4" s="199"/>
+      <c r="I4" s="199"/>
+      <c r="J4" s="199"/>
       <c r="K4" s="32"/>
     </row>
     <row r="5" spans="1:256" s="21" customFormat="1" ht="15.9" customHeight="1">
       <c r="A5" s="28"/>
-      <c r="B5" s="181" t="s">
+      <c r="B5" s="199" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="181"/>
-      <c r="D5" s="181"/>
-      <c r="E5" s="181"/>
-      <c r="F5" s="181"/>
-      <c r="G5" s="181"/>
-      <c r="H5" s="181"/>
-      <c r="I5" s="181"/>
-      <c r="J5" s="181"/>
+      <c r="C5" s="199"/>
+      <c r="D5" s="199"/>
+      <c r="E5" s="199"/>
+      <c r="F5" s="199"/>
+      <c r="G5" s="199"/>
+      <c r="H5" s="199"/>
+      <c r="I5" s="199"/>
+      <c r="J5" s="199"/>
       <c r="K5" s="32"/>
     </row>
     <row r="6" spans="1:256" s="21" customFormat="1" ht="31.8" customHeight="1">
       <c r="A6" s="29"/>
-      <c r="B6" s="206" t="s">
+      <c r="B6" s="187" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="206"/>
-      <c r="D6" s="206"/>
-      <c r="E6" s="206"/>
-      <c r="F6" s="206"/>
-      <c r="G6" s="206"/>
-      <c r="H6" s="206"/>
-      <c r="I6" s="206" t="str">
+      <c r="C6" s="187"/>
+      <c r="D6" s="187"/>
+      <c r="E6" s="187"/>
+      <c r="F6" s="187"/>
+      <c r="G6" s="187"/>
+      <c r="H6" s="187"/>
+      <c r="I6" s="187" t="str">
         <f>Report!O6</f>
         <v>File No.5143</v>
       </c>
-      <c r="J6" s="206"/>
+      <c r="J6" s="187"/>
       <c r="K6" s="31"/>
     </row>
     <row r="7" spans="1:256" s="21" customFormat="1" ht="31.8" customHeight="1">
       <c r="A7" s="30"/>
-      <c r="B7" s="207" t="str">
+      <c r="B7" s="188" t="str">
         <f>Report!B7</f>
         <v>Project Spec :- Section 31 23 16.33 ( Excavation, Fill and Subgrade)</v>
       </c>
-      <c r="C7" s="207"/>
-      <c r="D7" s="207"/>
-      <c r="E7" s="207"/>
-      <c r="F7" s="207"/>
-      <c r="G7" s="207"/>
-      <c r="H7" s="207"/>
+      <c r="C7" s="188"/>
+      <c r="D7" s="188"/>
+      <c r="E7" s="188"/>
+      <c r="F7" s="188"/>
+      <c r="G7" s="188"/>
+      <c r="H7" s="188"/>
       <c r="I7" s="98" t="str">
         <f>Report!O7</f>
         <v>Date :</v>
       </c>
-      <c r="J7" s="210">
+      <c r="J7" s="192">
         <f>Report!P7</f>
         <v>45906</v>
       </c>
-      <c r="K7" s="211"/>
+      <c r="K7" s="193"/>
     </row>
     <row r="8" spans="1:256" s="20" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A8" s="190" t="s">
+      <c r="A8" s="208" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="191"/>
-      <c r="C8" s="191"/>
-      <c r="D8" s="191"/>
-      <c r="E8" s="191"/>
-      <c r="F8" s="191"/>
-      <c r="G8" s="191"/>
-      <c r="H8" s="191"/>
-      <c r="I8" s="191"/>
-      <c r="J8" s="191"/>
-      <c r="K8" s="192"/>
+      <c r="B8" s="209"/>
+      <c r="C8" s="209"/>
+      <c r="D8" s="209"/>
+      <c r="E8" s="209"/>
+      <c r="F8" s="209"/>
+      <c r="G8" s="209"/>
+      <c r="H8" s="209"/>
+      <c r="I8" s="209"/>
+      <c r="J8" s="209"/>
+      <c r="K8" s="210"/>
     </row>
     <row r="9" spans="1:256" s="15" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A9" s="193" t="s">
+      <c r="A9" s="211" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="194"/>
-      <c r="C9" s="194"/>
-      <c r="D9" s="194"/>
-      <c r="E9" s="194"/>
-      <c r="F9" s="194"/>
-      <c r="G9" s="194"/>
-      <c r="H9" s="194"/>
-      <c r="I9" s="194"/>
-      <c r="J9" s="194"/>
-      <c r="K9" s="195"/>
+      <c r="B9" s="212"/>
+      <c r="C9" s="212"/>
+      <c r="D9" s="212"/>
+      <c r="E9" s="212"/>
+      <c r="F9" s="212"/>
+      <c r="G9" s="212"/>
+      <c r="H9" s="212"/>
+      <c r="I9" s="212"/>
+      <c r="J9" s="212"/>
+      <c r="K9" s="213"/>
     </row>
     <row r="10" spans="1:256" s="15" customFormat="1" ht="22.8" customHeight="1">
       <c r="A10" s="56"/>
       <c r="B10" s="19"/>
-      <c r="C10" s="212" t="str">
+      <c r="C10" s="194" t="str">
         <f>Report!B11</f>
         <v>Sample delivery date:</v>
       </c>
-      <c r="D10" s="212"/>
-      <c r="E10" s="215">
+      <c r="D10" s="194"/>
+      <c r="E10" s="197">
         <v>45900</v>
       </c>
-      <c r="F10" s="215"/>
+      <c r="F10" s="197"/>
       <c r="G10" s="99"/>
       <c r="H10" s="80"/>
       <c r="I10" s="80"/>
@@ -4499,19 +4498,19 @@
     <row r="11" spans="1:256" s="21" customFormat="1" ht="22.8" customHeight="1">
       <c r="A11" s="28"/>
       <c r="B11" s="3"/>
-      <c r="C11" s="213" t="str">
+      <c r="C11" s="195" t="str">
         <f>Report!B12</f>
         <v xml:space="preserve">Source of material :- </v>
       </c>
-      <c r="D11" s="213"/>
-      <c r="E11" s="216" t="str">
+      <c r="D11" s="195"/>
+      <c r="E11" s="198" t="str">
         <f>Report!F12</f>
         <v>Saleh Swiker Soil 70% + Swiker Sand 30%</v>
       </c>
-      <c r="F11" s="216"/>
-      <c r="G11" s="216"/>
-      <c r="H11" s="216"/>
-      <c r="I11" s="216"/>
+      <c r="F11" s="198"/>
+      <c r="G11" s="198"/>
+      <c r="H11" s="198"/>
+      <c r="I11" s="198"/>
       <c r="J11" s="34"/>
       <c r="K11" s="39"/>
       <c r="L11" s="1"/>
@@ -4519,12 +4518,12 @@
     <row r="12" spans="1:256" s="21" customFormat="1" ht="22.8" customHeight="1">
       <c r="A12" s="28"/>
       <c r="B12" s="81"/>
-      <c r="C12" s="214" t="str">
+      <c r="C12" s="196" t="str">
         <f>Report!B13</f>
         <v xml:space="preserve">Description of the Tested Materials :- </v>
       </c>
-      <c r="D12" s="214"/>
-      <c r="E12" s="214"/>
+      <c r="D12" s="196"/>
+      <c r="E12" s="196"/>
       <c r="F12" s="83" t="str">
         <f>Report!I13</f>
         <v>Fill / SM</v>
@@ -4832,67 +4831,67 @@
     <row r="16" spans="1:256" s="15" customFormat="1" ht="50.1" customHeight="1" thickTop="1">
       <c r="A16" s="62"/>
       <c r="B16" s="89"/>
-      <c r="C16" s="196" t="s">
+      <c r="C16" s="214" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="197"/>
-      <c r="E16" s="197" t="s">
+      <c r="D16" s="189"/>
+      <c r="E16" s="189" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="198"/>
-      <c r="G16" s="197" t="s">
+      <c r="F16" s="215"/>
+      <c r="G16" s="189" t="s">
         <v>14</v>
       </c>
-      <c r="H16" s="198"/>
-      <c r="I16" s="197" t="s">
+      <c r="H16" s="215"/>
+      <c r="I16" s="189" t="s">
         <v>13</v>
       </c>
-      <c r="J16" s="208"/>
+      <c r="J16" s="190"/>
       <c r="K16" s="64"/>
     </row>
     <row r="17" spans="1:12" s="15" customFormat="1" ht="58.8" customHeight="1" thickBot="1">
       <c r="A17" s="62"/>
       <c r="B17" s="89"/>
-      <c r="C17" s="186">
+      <c r="C17" s="204">
         <f>Report!E15</f>
         <v>50</v>
       </c>
-      <c r="D17" s="187"/>
-      <c r="E17" s="188">
+      <c r="D17" s="205"/>
+      <c r="E17" s="206">
         <f>Report!P13</f>
         <v>0</v>
       </c>
-      <c r="F17" s="188"/>
-      <c r="G17" s="188" t="s">
+      <c r="F17" s="206"/>
+      <c r="G17" s="206" t="s">
         <v>23</v>
       </c>
-      <c r="H17" s="188"/>
-      <c r="I17" s="188">
+      <c r="H17" s="206"/>
+      <c r="I17" s="206">
         <f>Report!P15</f>
         <v>0</v>
       </c>
-      <c r="J17" s="189"/>
+      <c r="J17" s="207"/>
       <c r="K17" s="64"/>
     </row>
     <row r="18" spans="1:12" s="15" customFormat="1" ht="39" customHeight="1" thickTop="1" thickBot="1">
       <c r="A18" s="65"/>
       <c r="B18" s="91"/>
-      <c r="C18" s="182" t="s">
+      <c r="C18" s="200" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="183"/>
-      <c r="E18" s="184" t="s">
+      <c r="D18" s="201"/>
+      <c r="E18" s="202" t="s">
         <v>38</v>
       </c>
-      <c r="F18" s="184"/>
-      <c r="G18" s="184" t="s">
+      <c r="F18" s="202"/>
+      <c r="G18" s="202" t="s">
         <v>34</v>
       </c>
-      <c r="H18" s="184"/>
-      <c r="I18" s="184" t="s">
+      <c r="H18" s="202"/>
+      <c r="I18" s="202" t="s">
         <v>39</v>
       </c>
-      <c r="J18" s="185"/>
+      <c r="J18" s="203"/>
       <c r="K18" s="66"/>
     </row>
     <row r="19" spans="1:12" s="15" customFormat="1" ht="62.4" customHeight="1" thickTop="1">
@@ -4930,31 +4929,31 @@
     </row>
     <row r="22" spans="1:12" s="16" customFormat="1" ht="27.6" customHeight="1">
       <c r="A22" s="68"/>
-      <c r="B22" s="209" t="str">
+      <c r="B22" s="191" t="str">
         <f>Report!B38</f>
         <v>The sample complies with the project specifications outlined in Section 31 23 16.33, Part 2, Item 2.1.B regarding suitable materials used for the construction of fill under pavements.</v>
       </c>
-      <c r="C22" s="209"/>
-      <c r="D22" s="209"/>
-      <c r="E22" s="209"/>
-      <c r="F22" s="209"/>
-      <c r="G22" s="209"/>
-      <c r="H22" s="209"/>
-      <c r="I22" s="209"/>
-      <c r="J22" s="209"/>
+      <c r="C22" s="191"/>
+      <c r="D22" s="191"/>
+      <c r="E22" s="191"/>
+      <c r="F22" s="191"/>
+      <c r="G22" s="191"/>
+      <c r="H22" s="191"/>
+      <c r="I22" s="191"/>
+      <c r="J22" s="191"/>
       <c r="K22" s="69"/>
     </row>
     <row r="23" spans="1:12" s="15" customFormat="1" ht="27.6" customHeight="1">
       <c r="A23" s="70"/>
-      <c r="B23" s="209"/>
-      <c r="C23" s="209"/>
-      <c r="D23" s="209"/>
-      <c r="E23" s="209"/>
-      <c r="F23" s="209"/>
-      <c r="G23" s="209"/>
-      <c r="H23" s="209"/>
-      <c r="I23" s="209"/>
-      <c r="J23" s="209"/>
+      <c r="B23" s="191"/>
+      <c r="C23" s="191"/>
+      <c r="D23" s="191"/>
+      <c r="E23" s="191"/>
+      <c r="F23" s="191"/>
+      <c r="G23" s="191"/>
+      <c r="H23" s="191"/>
+      <c r="I23" s="191"/>
+      <c r="J23" s="191"/>
       <c r="K23" s="66"/>
     </row>
     <row r="24" spans="1:12" s="15" customFormat="1" ht="30" customHeight="1" thickBot="1">
@@ -4971,13 +4970,13 @@
       <c r="D25" s="14"/>
       <c r="E25" s="14"/>
       <c r="F25" s="14"/>
-      <c r="G25" s="205" t="str">
+      <c r="G25" s="186" t="str">
         <f>Report!K40</f>
         <v>Dept. Manager : Eng. Reda El Raheb</v>
       </c>
-      <c r="H25" s="205"/>
-      <c r="I25" s="205"/>
-      <c r="J25" s="205"/>
+      <c r="H25" s="186"/>
+      <c r="I25" s="186"/>
+      <c r="J25" s="186"/>
       <c r="K25" s="73"/>
       <c r="L25" s="12"/>
     </row>
@@ -5149,6 +5148,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="B5:J5"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="A8:K8"/>
+    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A3:K3"/>
@@ -5165,20 +5178,6 @@
     <mergeCell ref="E10:F10"/>
     <mergeCell ref="E11:I11"/>
     <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B5:J5"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="A8:K8"/>
-    <mergeCell ref="A9:K9"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.5" header="0" footer="0"/>
@@ -5214,17 +5213,17 @@
   <sheetData>
     <row r="1" spans="1:19" ht="20.100000000000001" customHeight="1">
       <c r="A1" s="103"/>
-      <c r="B1" s="235" t="s">
+      <c r="B1" s="219" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="235"/>
-      <c r="D1" s="235"/>
-      <c r="E1" s="235"/>
-      <c r="F1" s="235"/>
-      <c r="G1" s="235"/>
-      <c r="H1" s="235"/>
-      <c r="I1" s="235"/>
-      <c r="J1" s="236"/>
+      <c r="C1" s="219"/>
+      <c r="D1" s="219"/>
+      <c r="E1" s="219"/>
+      <c r="F1" s="219"/>
+      <c r="G1" s="219"/>
+      <c r="H1" s="219"/>
+      <c r="I1" s="219"/>
+      <c r="J1" s="220"/>
     </row>
     <row r="2" spans="1:19" ht="9.9" customHeight="1">
       <c r="A2" s="28"/>
@@ -5240,69 +5239,69 @@
     </row>
     <row r="3" spans="1:19" ht="15.9" customHeight="1">
       <c r="A3" s="28"/>
-      <c r="B3" s="237" t="s">
+      <c r="B3" s="221" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="237"/>
-      <c r="D3" s="237"/>
-      <c r="E3" s="237"/>
-      <c r="F3" s="237"/>
-      <c r="G3" s="237"/>
-      <c r="H3" s="237"/>
-      <c r="I3" s="237"/>
-      <c r="J3" s="238"/>
+      <c r="C3" s="221"/>
+      <c r="D3" s="221"/>
+      <c r="E3" s="221"/>
+      <c r="F3" s="221"/>
+      <c r="G3" s="221"/>
+      <c r="H3" s="221"/>
+      <c r="I3" s="221"/>
+      <c r="J3" s="222"/>
     </row>
     <row r="4" spans="1:19" ht="15.9" customHeight="1">
       <c r="A4" s="28"/>
-      <c r="B4" s="237" t="s">
+      <c r="B4" s="221" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="237"/>
-      <c r="D4" s="237"/>
-      <c r="E4" s="237"/>
-      <c r="F4" s="237"/>
-      <c r="G4" s="237"/>
-      <c r="H4" s="237"/>
-      <c r="I4" s="237"/>
-      <c r="J4" s="238"/>
+      <c r="C4" s="221"/>
+      <c r="D4" s="221"/>
+      <c r="E4" s="221"/>
+      <c r="F4" s="221"/>
+      <c r="G4" s="221"/>
+      <c r="H4" s="221"/>
+      <c r="I4" s="221"/>
+      <c r="J4" s="222"/>
     </row>
     <row r="5" spans="1:19" ht="15.9" customHeight="1">
       <c r="A5" s="28"/>
-      <c r="B5" s="181" t="s">
+      <c r="B5" s="199" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="181"/>
-      <c r="D5" s="181"/>
-      <c r="E5" s="181"/>
-      <c r="F5" s="181"/>
-      <c r="G5" s="181"/>
-      <c r="H5" s="181"/>
-      <c r="I5" s="181"/>
-      <c r="J5" s="239"/>
+      <c r="C5" s="199"/>
+      <c r="D5" s="199"/>
+      <c r="E5" s="199"/>
+      <c r="F5" s="199"/>
+      <c r="G5" s="199"/>
+      <c r="H5" s="199"/>
+      <c r="I5" s="199"/>
+      <c r="J5" s="223"/>
     </row>
     <row r="6" spans="1:19" ht="15.6" customHeight="1">
       <c r="A6" s="28"/>
-      <c r="B6" s="181" t="s">
+      <c r="B6" s="199" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="181"/>
-      <c r="D6" s="181"/>
-      <c r="E6" s="181"/>
-      <c r="F6" s="181"/>
-      <c r="G6" s="181"/>
-      <c r="H6" s="181"/>
-      <c r="I6" s="181"/>
-      <c r="J6" s="239"/>
+      <c r="C6" s="199"/>
+      <c r="D6" s="199"/>
+      <c r="E6" s="199"/>
+      <c r="F6" s="199"/>
+      <c r="G6" s="199"/>
+      <c r="H6" s="199"/>
+      <c r="I6" s="199"/>
+      <c r="J6" s="223"/>
     </row>
     <row r="7" spans="1:19" ht="18" customHeight="1">
       <c r="A7" s="29"/>
-      <c r="B7" s="233" t="s">
+      <c r="B7" s="217" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="233"/>
-      <c r="D7" s="233"/>
-      <c r="E7" s="233"/>
-      <c r="F7" s="233"/>
+      <c r="C7" s="217"/>
+      <c r="D7" s="217"/>
+      <c r="E7" s="217"/>
+      <c r="F7" s="217"/>
       <c r="G7" s="105"/>
       <c r="H7" s="106"/>
       <c r="I7" s="105" t="s">
@@ -5312,102 +5311,103 @@
     </row>
     <row r="8" spans="1:19" ht="18" customHeight="1">
       <c r="A8" s="30"/>
-      <c r="B8" s="234" t="s">
+      <c r="B8" s="218" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="234"/>
-      <c r="D8" s="234"/>
-      <c r="E8" s="234"/>
-      <c r="F8" s="234"/>
-      <c r="G8" s="234"/>
+      <c r="C8" s="218"/>
+      <c r="D8" s="218"/>
+      <c r="E8" s="218"/>
+      <c r="F8" s="218"/>
+      <c r="G8" s="218"/>
       <c r="H8" s="108"/>
-      <c r="I8" s="125" t="s">
-        <v>61</v>
+      <c r="I8" s="239" t="str">
+        <f>"Date: " &amp; TEXT(Report!P7,"dd/mm/yyyy")</f>
+        <v>Date: 06/09/2025</v>
       </c>
       <c r="J8" s="109"/>
     </row>
     <row r="9" spans="1:19" ht="24.6" customHeight="1">
       <c r="A9" s="29"/>
-      <c r="B9" s="232" t="s">
+      <c r="B9" s="216" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="232"/>
-      <c r="D9" s="232"/>
-      <c r="E9" s="232"/>
-      <c r="F9" s="232"/>
-      <c r="G9" s="232"/>
-      <c r="H9" s="232"/>
-      <c r="I9" s="232"/>
+      <c r="C9" s="216"/>
+      <c r="D9" s="216"/>
+      <c r="E9" s="216"/>
+      <c r="F9" s="216"/>
+      <c r="G9" s="216"/>
+      <c r="H9" s="216"/>
+      <c r="I9" s="216"/>
       <c r="J9" s="31"/>
     </row>
     <row r="10" spans="1:19" ht="24.6" customHeight="1">
       <c r="A10" s="30"/>
-      <c r="B10" s="220" t="s">
+      <c r="B10" s="227" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="220"/>
-      <c r="D10" s="220"/>
-      <c r="E10" s="220"/>
-      <c r="F10" s="220"/>
-      <c r="G10" s="220"/>
-      <c r="H10" s="220"/>
-      <c r="I10" s="220"/>
+      <c r="C10" s="227"/>
+      <c r="D10" s="227"/>
+      <c r="E10" s="227"/>
+      <c r="F10" s="227"/>
+      <c r="G10" s="227"/>
+      <c r="H10" s="227"/>
+      <c r="I10" s="227"/>
       <c r="J10" s="109"/>
     </row>
     <row r="11" spans="1:19" ht="20.399999999999999" customHeight="1">
       <c r="A11" s="28"/>
-      <c r="B11" s="223" t="s">
+      <c r="B11" s="230" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="223"/>
-      <c r="D11" s="223"/>
-      <c r="E11" s="223"/>
-      <c r="F11" s="224">
+      <c r="C11" s="230"/>
+      <c r="D11" s="230"/>
+      <c r="E11" s="230"/>
+      <c r="F11" s="231">
         <f>Report!F11</f>
         <v>45900</v>
       </c>
-      <c r="G11" s="224"/>
+      <c r="G11" s="231"/>
       <c r="J11" s="32"/>
     </row>
     <row r="12" spans="1:19" ht="20.399999999999999" customHeight="1">
       <c r="A12" s="28"/>
-      <c r="B12" s="225" t="s">
+      <c r="B12" s="232" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="225"/>
-      <c r="D12" s="225"/>
-      <c r="E12" s="226" t="str">
+      <c r="C12" s="232"/>
+      <c r="D12" s="232"/>
+      <c r="E12" s="233" t="str">
         <f>Report!F12</f>
         <v>Saleh Swiker Soil 70% + Swiker Sand 30%</v>
       </c>
-      <c r="F12" s="226"/>
-      <c r="G12" s="226"/>
-      <c r="H12" s="126"/>
+      <c r="F12" s="233"/>
+      <c r="G12" s="233"/>
+      <c r="H12" s="125"/>
       <c r="J12" s="32"/>
     </row>
     <row r="13" spans="1:19" ht="20.399999999999999" customHeight="1">
       <c r="A13" s="28"/>
-      <c r="B13" s="213" t="s">
+      <c r="B13" s="195" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="213"/>
-      <c r="D13" s="213"/>
-      <c r="E13" s="213"/>
-      <c r="F13" s="216" t="str">
+      <c r="C13" s="195"/>
+      <c r="D13" s="195"/>
+      <c r="E13" s="195"/>
+      <c r="F13" s="198" t="str">
         <f>Report!I13</f>
         <v>Fill / SM</v>
       </c>
-      <c r="G13" s="216"/>
+      <c r="G13" s="198"/>
       <c r="H13" s="22"/>
       <c r="J13" s="32"/>
     </row>
     <row r="14" spans="1:19" ht="20.399999999999999" customHeight="1">
       <c r="A14" s="28"/>
-      <c r="B14" s="213" t="s">
+      <c r="B14" s="195" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="213"/>
-      <c r="D14" s="213"/>
+      <c r="C14" s="195"/>
+      <c r="D14" s="195"/>
       <c r="E14" s="33">
         <f>Report!E14</f>
         <v>3</v>
@@ -5419,18 +5419,18 @@
     </row>
     <row r="15" spans="1:19" ht="20.399999999999999" customHeight="1">
       <c r="A15" s="28"/>
-      <c r="B15" s="213" t="s">
+      <c r="B15" s="195" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="213"/>
-      <c r="D15" s="213"/>
+      <c r="C15" s="195"/>
+      <c r="D15" s="195"/>
       <c r="E15" s="33">
         <f>Report!E15</f>
         <v>50</v>
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="34"/>
-      <c r="H15" s="127"/>
+      <c r="H15" s="126"/>
       <c r="J15" s="32"/>
       <c r="S15" s="22"/>
     </row>
@@ -5447,11 +5447,11 @@
     </row>
     <row r="17" spans="1:11" ht="46.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A17" s="28"/>
-      <c r="B17" s="221" t="s">
+      <c r="B17" s="228" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="222"/>
-      <c r="D17" s="222"/>
+      <c r="C17" s="229"/>
+      <c r="D17" s="229"/>
       <c r="E17" s="110">
         <v>2.145</v>
       </c>
@@ -5469,11 +5469,11 @@
     </row>
     <row r="18" spans="1:11" ht="35.1" customHeight="1" thickTop="1">
       <c r="A18" s="28"/>
-      <c r="B18" s="227" t="s">
+      <c r="B18" s="234" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="228"/>
-      <c r="D18" s="228"/>
+      <c r="C18" s="235"/>
+      <c r="D18" s="235"/>
       <c r="E18" s="112">
         <v>4.7</v>
       </c>
@@ -5491,11 +5491,11 @@
     </row>
     <row r="19" spans="1:11" ht="48" customHeight="1" thickBot="1">
       <c r="A19" s="28"/>
-      <c r="B19" s="229" t="s">
+      <c r="B19" s="236" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="230"/>
-      <c r="D19" s="230"/>
+      <c r="C19" s="237"/>
+      <c r="D19" s="237"/>
       <c r="E19" s="114">
         <f>E17/(1+E18/100)</f>
         <v>2.0487106017191978</v>
@@ -5582,58 +5582,58 @@
     <row r="35" spans="1:12" ht="15.9" customHeight="1">
       <c r="A35" s="116"/>
       <c r="B35" s="22"/>
-      <c r="D35" s="128"/>
-      <c r="E35" s="128"/>
-      <c r="F35" s="128"/>
-      <c r="G35" s="128"/>
-      <c r="H35" s="128"/>
-      <c r="I35" s="128"/>
+      <c r="D35" s="127"/>
+      <c r="E35" s="127"/>
+      <c r="F35" s="127"/>
+      <c r="G35" s="127"/>
+      <c r="H35" s="127"/>
+      <c r="I35" s="127"/>
       <c r="J35" s="117"/>
     </row>
     <row r="36" spans="1:12" ht="22.2" customHeight="1">
       <c r="A36" s="116"/>
       <c r="B36" s="22"/>
-      <c r="C36" s="129"/>
+      <c r="C36" s="128"/>
       <c r="D36" s="44" t="s">
         <v>56</v>
       </c>
       <c r="E36" s="44"/>
-      <c r="F36" s="130">
+      <c r="F36" s="129">
         <v>2.1179999999999999</v>
       </c>
       <c r="G36" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="I36" s="128"/>
+      <c r="I36" s="127"/>
       <c r="J36" s="117"/>
     </row>
     <row r="37" spans="1:12" ht="22.2" customHeight="1">
       <c r="A37" s="116"/>
       <c r="B37" s="22"/>
-      <c r="C37" s="129"/>
-      <c r="D37" s="231" t="s">
+      <c r="C37" s="128"/>
+      <c r="D37" s="238" t="s">
         <v>58</v>
       </c>
-      <c r="E37" s="231"/>
-      <c r="F37" s="131">
+      <c r="E37" s="238"/>
+      <c r="F37" s="130">
         <v>6.6</v>
       </c>
-      <c r="G37" s="132" t="s">
+      <c r="G37" s="131" t="s">
         <v>59</v>
       </c>
-      <c r="H37" s="133"/>
-      <c r="I37" s="128"/>
+      <c r="H37" s="132"/>
+      <c r="I37" s="127"/>
       <c r="J37" s="117"/>
     </row>
     <row r="38" spans="1:12" ht="15.9" customHeight="1">
       <c r="A38" s="116"/>
       <c r="B38" s="22"/>
-      <c r="D38" s="134"/>
-      <c r="E38" s="128"/>
-      <c r="F38" s="131"/>
-      <c r="G38" s="128"/>
-      <c r="H38" s="128"/>
-      <c r="I38" s="128"/>
+      <c r="D38" s="133"/>
+      <c r="E38" s="127"/>
+      <c r="F38" s="130"/>
+      <c r="G38" s="127"/>
+      <c r="H38" s="127"/>
+      <c r="I38" s="127"/>
       <c r="J38" s="117"/>
     </row>
     <row r="39" spans="1:12" ht="8.1" customHeight="1">
@@ -5642,29 +5642,29 @@
     </row>
     <row r="40" spans="1:12" ht="28.2" customHeight="1">
       <c r="A40" s="29"/>
-      <c r="B40" s="164" t="str">
+      <c r="B40" s="153" t="str">
         <f>Report!B40</f>
         <v>Prepared by : Eng. Alaa Hassan</v>
       </c>
-      <c r="C40" s="164"/>
-      <c r="D40" s="164"/>
-      <c r="E40" s="164"/>
+      <c r="C40" s="153"/>
+      <c r="D40" s="153"/>
+      <c r="E40" s="153"/>
       <c r="F40" s="118"/>
-      <c r="G40" s="217" t="str">
+      <c r="G40" s="224" t="str">
         <f>Report!K40</f>
         <v>Dept. Manager : Eng. Reda El Raheb</v>
       </c>
-      <c r="H40" s="217"/>
-      <c r="I40" s="217"/>
-      <c r="J40" s="218"/>
+      <c r="H40" s="224"/>
+      <c r="I40" s="224"/>
+      <c r="J40" s="225"/>
     </row>
     <row r="41" spans="1:12" ht="28.2" customHeight="1" thickBot="1">
       <c r="A41" s="119"/>
-      <c r="B41" s="219"/>
-      <c r="C41" s="219"/>
-      <c r="D41" s="219"/>
-      <c r="E41" s="219"/>
-      <c r="F41" s="219"/>
+      <c r="B41" s="226"/>
+      <c r="C41" s="226"/>
+      <c r="D41" s="226"/>
+      <c r="E41" s="226"/>
+      <c r="F41" s="226"/>
       <c r="G41" s="120"/>
       <c r="H41" s="120"/>
       <c r="I41" s="120"/>
@@ -5677,44 +5677,44 @@
       <c r="L43" s="122"/>
     </row>
     <row r="44" spans="1:12" ht="15.75" customHeight="1">
-      <c r="F44" s="136">
+      <c r="F44" s="135">
         <f>F37</f>
         <v>6.6</v>
       </c>
-      <c r="G44" s="136">
+      <c r="G44" s="135">
         <f>F37</f>
         <v>6.6</v>
       </c>
-      <c r="H44" s="136">
+      <c r="H44" s="135">
         <v>0</v>
       </c>
       <c r="L44" s="122"/>
     </row>
     <row r="45" spans="1:12" ht="15.75" customHeight="1">
-      <c r="F45" s="137">
+      <c r="F45" s="136">
         <f>F36</f>
         <v>2.1179999999999999</v>
       </c>
-      <c r="G45" s="137">
+      <c r="G45" s="136">
         <f>F36-(F36-E19)</f>
         <v>2.0487106017191978</v>
       </c>
-      <c r="H45" s="137">
+      <c r="H45" s="136">
         <f>F36</f>
         <v>2.1179999999999999</v>
       </c>
       <c r="L45" s="122"/>
     </row>
     <row r="46" spans="1:12" ht="15.75" customHeight="1">
-      <c r="F46" s="136"/>
-      <c r="G46" s="136"/>
-      <c r="H46" s="136"/>
+      <c r="F46" s="135"/>
+      <c r="G46" s="135"/>
+      <c r="H46" s="135"/>
       <c r="L46" s="122"/>
     </row>
     <row r="47" spans="1:12" ht="15.75" customHeight="1">
-      <c r="F47" s="136"/>
-      <c r="G47" s="136"/>
-      <c r="H47" s="137"/>
+      <c r="F47" s="135"/>
+      <c r="G47" s="135"/>
+      <c r="H47" s="136"/>
       <c r="L47" s="122"/>
     </row>
     <row r="48" spans="1:12" ht="15.75" customHeight="1">
@@ -5746,14 +5746,6 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <mergeCells count="24">
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B5:J5"/>
-    <mergeCell ref="B6:J6"/>
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="G40:J40"/>
     <mergeCell ref="B41:F41"/>
@@ -5770,6 +5762,14 @@
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="D37:E37"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B5:J5"/>
+    <mergeCell ref="B6:J6"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.196850393700787" right="0.196850393700787" top="0.196850393700787" bottom="0.196850393700787" header="0" footer="0"/>
